--- a/Alcopalet_Analisis.xlsx
+++ b/Alcopalet_Analisis.xlsx
@@ -3157,7 +3157,7 @@
         <v>397328.0</v>
       </c>
       <c r="D120" s="76" t="n">
-        <v>-287917</v>
+        <v>-169183</v>
       </c>
       <c r="E120" s="23" t="inlineStr">
         <is>
